--- a/TestFiles-prod-sanity/MmpTemplate/[MLB]MmpStatement-NB.xlsx
+++ b/TestFiles-prod-sanity/MmpTemplate/[MLB]MmpStatement-NB.xlsx
@@ -76,10 +76,10 @@
     <t>Premium</t>
   </si>
   <si>
-    <t>TestAgent0065</t>
-  </si>
-  <si>
-    <t>90065</t>
+    <t>TestAgent0122</t>
+  </si>
+  <si>
+    <t>90122</t>
   </si>
   <si>
     <t>232 E KING ST2 , ,, MALVERN, PA, 19355</t>
@@ -88,7 +88,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>ATENA-MMP-TEST-A086</t>
+    <t>ATENA-MMP-TEST-A122</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
